--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-019.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-019.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CFB18F-1BDD-40E7-B455-C22D3FC3626D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BD9AFC-D164-47C4-AA15-9CFE339772FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{8F48421F-263C-4EF6-A482-1F2A0C82BA6C}"/>
+    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{5EC7F62D-A81D-4496-AD26-7CD538541B7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MyName" localSheetId="0">Sheet1!$A$1</definedName>
+    <definedName name="MyName" localSheetId="0">Sheet1!$B$1</definedName>
+    <definedName name="MyName">Sheet1!$A$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -404,7 +405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55C819E-D22C-4357-8444-B961AB3FE3C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B196CD67-D496-4491-9918-4596BA7426FD}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -420,7 +421,7 @@
       </c>
       <c r="D1">
         <f>MyName</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
